--- a/_sources/cdifProperties/cdifCore/cdifCore_properties.xlsx
+++ b/_sources/cdifProperties/cdifCore/cdifCore_properties.xlsx
@@ -8,27 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/CDIF/metadataBuildingBlocksFork/_sources/cdifProperties/cdifCore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="11_05052B09E4C4201FDF7C04F5839C58910C8DF9A7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91D89B7-0539-412E-B719-E6857151C2C8}"/>
+  <xr:revisionPtr revIDLastSave="618" documentId="11_05052B09E4C4201FDF7C04F5839C58910C8DF9A7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C45AB001-6645-4ADB-A194-EA4E12E47361}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="525" windowWidth="21825" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="810" windowWidth="27270" windowHeight="16020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="propertyTree" sheetId="9" r:id="rId1"/>
-    <sheet name="cdifCore" sheetId="1" r:id="rId2"/>
-    <sheet name="identifier" sheetId="2" r:id="rId3"/>
-    <sheet name="labeledLink" sheetId="3" r:id="rId4"/>
-    <sheet name="dataDownload" sheetId="4" r:id="rId5"/>
-    <sheet name="cdifCatalogRecord" sheetId="5" r:id="rId6"/>
-    <sheet name="person" sheetId="6" r:id="rId7"/>
-    <sheet name="organization" sheetId="7" r:id="rId8"/>
-    <sheet name="definedTerm" sheetId="8" r:id="rId9"/>
+    <sheet name="propertyTree_2" sheetId="10" r:id="rId2"/>
+    <sheet name="cdifCore" sheetId="1" r:id="rId3"/>
+    <sheet name="identifier" sheetId="2" r:id="rId4"/>
+    <sheet name="labeledLink" sheetId="3" r:id="rId5"/>
+    <sheet name="dataDownload" sheetId="4" r:id="rId6"/>
+    <sheet name="cdifCatalogRecord" sheetId="5" r:id="rId7"/>
+    <sheet name="person" sheetId="6" r:id="rId8"/>
+    <sheet name="organization" sheetId="7" r:id="rId9"/>
+    <sheet name="definedTerm" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="239">
   <si>
     <t>Field Name</t>
   </si>
@@ -561,13 +562,214 @@
   </si>
   <si>
     <t>object/datatype</t>
+  </si>
+  <si>
+    <t>schema:name -- string</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:Dataset)</t>
+  </si>
+  <si>
+    <t>@id -- string(uri)</t>
+  </si>
+  <si>
+    <t>@context -- standard cdif context</t>
+  </si>
+  <si>
+    <t>schema:identifier -- CHOICE</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:PropertyValue)</t>
+  </si>
+  <si>
+    <t>schema:propertyID -- string</t>
+  </si>
+  <si>
+    <t>schema:value -- string</t>
+  </si>
+  <si>
+    <t>schema:url -- string(uri)</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:CreativeWork)</t>
+  </si>
+  <si>
+    <t>schema:dateModified -- string(date)</t>
+  </si>
+  <si>
+    <t>schema:description -- string</t>
+  </si>
+  <si>
+    <t>schema:url -- string(URI)</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:DataDownload)</t>
+  </si>
+  <si>
+    <t>schema:contentUrl -- string(uri)</t>
+  </si>
+  <si>
+    <t>schema:encodingFormat -- [string]</t>
+  </si>
+  <si>
+    <t>algorithm -- string</t>
+  </si>
+  <si>
+    <t>value -- string</t>
+  </si>
+  <si>
+    <t>dcterms:conformsTo -- [object reference]</t>
+  </si>
+  <si>
+    <t>options</t>
+  </si>
+  <si>
+    <t>schema:serviceType -- CHOICE</t>
+  </si>
+  <si>
+    <t>schema:termsOfService -- CHOICE</t>
+  </si>
+  <si>
+    <t>schema:documentation -- CHOICE</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:Organization)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>schema:sameAs -- [CHOICE]</t>
+  </si>
+  <si>
+    <t>objectReference</t>
+  </si>
+  <si>
+    <t>spdx:checksum -- object</t>
+  </si>
+  <si>
+    <t>schema:contactPoint -- object</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:ContactPoint)</t>
+  </si>
+  <si>
+    <t>schema:email -- string</t>
+  </si>
+  <si>
+    <t>schema:additionalType -- CHOICE</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:DefinedTerm)</t>
+  </si>
+  <si>
+    <t>schema:inDefinedTermSet -- string</t>
+  </si>
+  <si>
+    <t>schema:termCode -- string</t>
+  </si>
+  <si>
+    <t>schema:alternateName -- string</t>
+  </si>
+  <si>
+    <t>schema:conditionsOfAccess -- [CHOICE]</t>
+  </si>
+  <si>
+    <t>schema:subjectOf -- object</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schemaWebAPI)</t>
+  </si>
+  <si>
+    <t>schema:about -- object reference</t>
+  </si>
+  <si>
+    <t>schema:maintainer -- CHOICE</t>
+  </si>
+  <si>
+    <t>schema:sdDatePublished -- string(date0</t>
+  </si>
+  <si>
+    <t>schema:includedInDataCatalog -- object</t>
+  </si>
+  <si>
+    <t>schema:license -- [CHOICE]</t>
+  </si>
+  <si>
+    <t>schema:potentialAction -- object</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:Action)</t>
+  </si>
+  <si>
+    <t>schema:target -- object</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:EntryPoint)</t>
+  </si>
+  <si>
+    <t>schema:urlTemplate -- string</t>
+  </si>
+  <si>
+    <t>schem:httpMethod -- string</t>
+  </si>
+  <si>
+    <t>schema:contentType -- [string]</t>
+  </si>
+  <si>
+    <t>schema:result -- object</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:DataFeed)</t>
+  </si>
+  <si>
+    <t>schema:object -- object</t>
+  </si>
+  <si>
+    <t>schema:query-input-- object</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:PropertyValueSpecification)</t>
+  </si>
+  <si>
+    <t>schema:valueName -- string</t>
+  </si>
+  <si>
+    <t>schema:valueRequired -- boolean</t>
+  </si>
+  <si>
+    <t>schema: valuePattern -- string</t>
+  </si>
+  <si>
+    <t>schem:additionaltype -- [string](contains dcat:CatalogRecord)</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:DataCatalog)</t>
+  </si>
+  <si>
+    <t>schema:url -- string (uri)</t>
+  </si>
+  <si>
+    <t>schema:distribution --[ CHOICE]</t>
+  </si>
+  <si>
+    <t>@type -- [string](contains schema:Person)</t>
+  </si>
+  <si>
+    <t>enum --  "schema:FundingAgency",    "schema:Consortium",   "schema:Corporation",     "schema:EducationalOrganization",  "schema:FundingScheme",    "schema:GovernmentOrganization",     "schema:NGO",   "schema:Project",              "schema:ResearchOrganization"</t>
+  </si>
+  <si>
+    <t>enum --  "schema:FundingAgency",   "schema:Consortium", "schema:Corporation", "schema:EducationalOrganization",  "schema:FundingScheme", "schema:GovernmentOrganization",   "schema:NGO",     "schema:Project", "schema:ResearchOrganization"</t>
+  </si>
+  <si>
+    <t>schema:provider -- [CHOICE]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,6 +781,13 @@
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -607,7 +816,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -619,8 +828,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -722,6 +936,96 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD23B55B-A08B-4DC7-B6F3-C25AF7770EA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7524750" y="828675"/>
+          <a:ext cx="3743325" cy="1333500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>[..]</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> -- value is an array (JSON list)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>object  reference-- {@id:  URI}</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1336,13 +1640,13 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D41" s="2"/>
-      <c r="E41" s="5" t="s">
+      <c r="E41" t="s">
         <v>147</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1471,13 +1775,13 @@
       <c r="D60" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" t="s">
         <v>147</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1537,7 +1841,1714 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA49550-EF77-4056-861C-8540C54B7C2C}">
+  <dimension ref="A1:L212"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="37.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="29.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="10" max="10" width="38.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
+    <col min="12" max="12" width="39.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="C17" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="2"/>
+      <c r="C24" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D26" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D27" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="2"/>
+      <c r="D33" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D34" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D35" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D36" s="2"/>
+      <c r="F36" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F37" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D38" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D39" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E41" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E42" s="2"/>
+      <c r="F42" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E43" s="2"/>
+      <c r="F43" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E44" s="2"/>
+      <c r="F44" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E50" s="2"/>
+      <c r="F50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E51" s="2"/>
+      <c r="F51" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="52" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="J59" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="J60" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="J61" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="J62" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="5:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="69" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="72" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="73" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="75" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="I75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="I76" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E77" s="2"/>
+      <c r="F77" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="78" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="H78" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="79" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E79" s="2"/>
+      <c r="F79" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="80" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E80" s="2"/>
+      <c r="G80" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E81" s="2"/>
+      <c r="G81" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E82" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E83" s="2"/>
+      <c r="F83" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E84" s="2"/>
+      <c r="F84" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E85" s="2"/>
+      <c r="F85" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E86" s="2"/>
+      <c r="F86" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E87" s="2"/>
+      <c r="F87" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E88" s="2"/>
+      <c r="F88" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C89" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D90" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D91" s="2"/>
+      <c r="E91" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D92" s="2"/>
+      <c r="E92" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D93" s="2"/>
+      <c r="F93" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D94" s="2"/>
+      <c r="F94" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G94" s="2"/>
+    </row>
+    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D95" s="2"/>
+      <c r="F95" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G95" s="2"/>
+    </row>
+    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D96" s="2"/>
+      <c r="F96" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D102" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E102" s="2"/>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D103" s="2"/>
+      <c r="E103" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D104" s="2"/>
+      <c r="E104" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D105" s="2"/>
+      <c r="F105" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D106" s="2"/>
+      <c r="F106" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D107" s="2"/>
+      <c r="F107" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>196</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E108" s="2"/>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D109" s="2"/>
+      <c r="E109" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D110" s="2"/>
+      <c r="E110" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D111" s="2"/>
+      <c r="F111" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D112" s="2"/>
+      <c r="F112" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="113" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D113" s="2"/>
+      <c r="F113" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="114" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D114" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="115" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="116" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="117" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="H117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="118" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="H118" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="119" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="H119" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="120" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="H120" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="121" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s">
+        <v>223</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="122" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="H122" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="123" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="H123" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="124" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s">
+        <v>225</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="125" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="H125" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="126" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s">
+        <v>226</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="127" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="H127" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="128" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="H128" s="7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="H129" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="H130" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B131" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="132" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B132" s="2"/>
+      <c r="D132" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D133" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F133" s="3"/>
+    </row>
+    <row r="134" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D134" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D135" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D136" s="2"/>
+      <c r="E136" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D137" s="2"/>
+      <c r="F137" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F138" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="139" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F139" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="140" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F140" s="2"/>
+      <c r="G140" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F141" s="2"/>
+      <c r="G141" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="142" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="143" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="144" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="145" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F145" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F146" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="147" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J147" s="2"/>
+      <c r="K147" s="2"/>
+    </row>
+    <row r="148" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J148" s="2"/>
+      <c r="K148" s="2"/>
+    </row>
+    <row r="149" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="150" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="151" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+      <c r="I151" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+      <c r="I152" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="153" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+      <c r="I153" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="154" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+      <c r="J154" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="155" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+      <c r="J155" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K155" s="2"/>
+    </row>
+    <row r="156" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="J156" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K156" s="2"/>
+    </row>
+    <row r="157" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+      <c r="J157" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="158" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+      <c r="J158" s="2"/>
+      <c r="K158" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+      <c r="J159" s="2"/>
+      <c r="K159" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="160" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+      <c r="J160" s="2"/>
+      <c r="K160" s="2"/>
+      <c r="L160" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="161" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+      <c r="J161" s="2"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="162" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+      <c r="J162" s="2"/>
+      <c r="K162" s="2"/>
+      <c r="L162" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="163" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="164" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+      <c r="I164" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+      <c r="I165" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="166" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+      <c r="I166" s="2"/>
+      <c r="J166" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="167" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+      <c r="I167" s="2"/>
+      <c r="J167" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="168" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+      <c r="I168" s="2"/>
+      <c r="J168" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="169" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="170" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="I170" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="I171" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="172" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F172" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="173" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F173" s="2"/>
+      <c r="H173" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="174" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F174" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="175" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="G175" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="G176" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="177" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E177" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="178" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E178" s="2"/>
+      <c r="F178" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
+    </row>
+    <row r="179" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E179" s="2"/>
+      <c r="F179" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H179" s="2"/>
+      <c r="I179" s="2"/>
+    </row>
+    <row r="180" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E180" s="2"/>
+      <c r="F180" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="181" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E181" s="2"/>
+      <c r="F181" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="182" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E182" s="2"/>
+      <c r="F182" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="183" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="185" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="186" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="H186" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="187" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="H187" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I187" s="2"/>
+    </row>
+    <row r="188" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="H188" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I188" s="2"/>
+    </row>
+    <row r="189" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="H189" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="190" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="H190" s="2"/>
+      <c r="I190" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="191" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
+      <c r="H191" s="2"/>
+      <c r="I191" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="192" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="H192" s="2"/>
+      <c r="I192" s="2"/>
+      <c r="J192" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="193" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="H193" s="2"/>
+      <c r="I193" s="2"/>
+      <c r="J193" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="194" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="H194" s="2"/>
+      <c r="I194" s="2"/>
+      <c r="J194" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="195" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="196" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="197" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="198" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+      <c r="H198" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="199" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="200" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E200" s="2"/>
+      <c r="F200" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="201" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E201" s="2"/>
+      <c r="G201" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="202" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E202" s="2"/>
+      <c r="G202" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="203" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D203" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="204" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D204" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E204" s="2"/>
+      <c r="F204" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="205" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="F205" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="206" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="F206" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="207" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="F207" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="208" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="F208" s="2"/>
+      <c r="G208" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="209" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F209" s="2"/>
+      <c r="G209" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="210" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F210" s="2"/>
+      <c r="H210" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="211" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F211" s="2"/>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="212" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F212" s="2"/>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1789,7 +3800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1902,7 +3913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2015,7 +4026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2219,7 +4230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2409,7 +4420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2468,7 +4479,7 @@
         <v>104</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
@@ -2613,7 +4624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2798,137 +4809,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="80" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>